--- a/cronograma_estudo.xlsx
+++ b/cronograma_estudo.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29415"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="351" documentId="11_7F4755BF84DCCE43E268565A8931F45BFA75341E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{702B5F84-4C30-48BA-BDBA-016B9E5B4762}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\study\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31A5A56-0A6A-4FB4-99BD-CA1BD3751B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mês 01" sheetId="1" r:id="rId1"/>
@@ -28,6 +33,9 @@
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -318,7 +326,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,115 +678,76 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -788,8 +757,47 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1126,91 +1134,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.42578125" customWidth="1"/>
     <col min="2" max="2" width="49.28515625" customWidth="1"/>
     <col min="3" max="4" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="47.25" customHeight="1">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" ht="84.75" customHeight="1">
+      <c r="D2" s="20"/>
+    </row>
+    <row r="3" spans="1:4" ht="84.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="15"/>
-    </row>
-    <row r="4" spans="1:4" ht="86.25" customHeight="1">
+      <c r="D3" s="22"/>
+    </row>
+    <row r="4" spans="1:4" ht="86.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="15"/>
-    </row>
-    <row r="5" spans="1:4" ht="72.75">
+      <c r="B4" s="18"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="22"/>
+    </row>
+    <row r="5" spans="1:4" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="15"/>
-    </row>
-    <row r="6" spans="1:4" ht="81" customHeight="1">
+      <c r="B5" s="18"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="22"/>
+    </row>
+    <row r="6" spans="1:4" ht="81" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="15"/>
-    </row>
-    <row r="7" spans="1:4" ht="268.5" customHeight="1">
-      <c r="B7" s="10"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="15"/>
-    </row>
-    <row r="8" spans="1:4" ht="18.75" customHeight="1">
-      <c r="A8" s="41" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="22"/>
+    </row>
+    <row r="7" spans="1:4" ht="268.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="22"/>
+    </row>
+    <row r="8" spans="1:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="43" t="s">
+      <c r="C8" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="37"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="C9" s="38" t="s">
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C9" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="39"/>
+      <c r="D9" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1228,7 +1236,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB8C816-419A-44CF-B7F4-EDAD470D4D44}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.7109375" customWidth="1"/>
     <col min="2" max="3" width="49.28515625" customWidth="1"/>
@@ -1236,16 +1244,16 @@
     <col min="5" max="5" width="40.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32.25" customHeight="1">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:5" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-    </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="47.25" customHeight="1">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>15</v>
       </c>
@@ -1255,66 +1263,66 @@
       <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="13"/>
-    </row>
-    <row r="3" spans="1:5" ht="68.25" customHeight="1">
-      <c r="A3" s="19" t="s">
+      <c r="E2" s="20"/>
+    </row>
+    <row r="3" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B3" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="45" t="s">
+      <c r="C3" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="15"/>
-    </row>
-    <row r="4" spans="1:5" ht="68.25" customHeight="1">
-      <c r="A4" s="20"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="46"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="15"/>
-    </row>
-    <row r="5" spans="1:5" ht="46.5" customHeight="1">
-      <c r="A5" s="20"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:5" ht="92.25" customHeight="1">
-      <c r="A6" s="20"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" spans="1:5" ht="409.5" customHeight="1">
-      <c r="A7" s="21"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="47"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18"/>
-    </row>
-    <row r="8" spans="1:5" ht="82.5" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="E3" s="22"/>
+    </row>
+    <row r="4" spans="1:5" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="22"/>
+    </row>
+    <row r="5" spans="1:5" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="22"/>
+    </row>
+    <row r="6" spans="1:5" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="22"/>
+    </row>
+    <row r="7" spans="1:5" ht="409.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="31"/>
+      <c r="B7" s="26"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="27"/>
+      <c r="E7" s="28"/>
+    </row>
+    <row r="8" spans="1:5" ht="82.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="7"/>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="44"/>
+      <c r="E8" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -1333,7 +1341,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06C733CA-55E7-43CE-AA90-6A83311A1DAF}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" customWidth="1"/>
     <col min="2" max="2" width="38.28515625" customWidth="1"/>
@@ -1341,60 +1349,60 @@
     <col min="4" max="4" width="7.5703125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="32.25" customHeight="1">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:4" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="27"/>
-    </row>
-    <row r="3" spans="1:4" ht="68.25" customHeight="1">
-      <c r="A3" s="28" t="s">
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="40"/>
+    </row>
+    <row r="3" spans="1:4" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="29"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-    </row>
-    <row r="4" spans="1:4" ht="68.25" customHeight="1">
-      <c r="A4" s="31"/>
-      <c r="B4" s="14"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="32"/>
-    </row>
-    <row r="5" spans="1:4" ht="15" customHeight="1">
-      <c r="A5" s="31"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="14"/>
-      <c r="D5" s="32"/>
-    </row>
-    <row r="6" spans="1:4" ht="92.25" customHeight="1">
-      <c r="A6" s="31"/>
-      <c r="B6" s="14"/>
-      <c r="C6" s="14"/>
-      <c r="D6" s="32"/>
-    </row>
-    <row r="7" spans="1:4" ht="339" customHeight="1">
-      <c r="A7" s="33"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="35"/>
-    </row>
-    <row r="8" spans="1:4" ht="29.25" customHeight="1">
-      <c r="A8" s="44" t="s">
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="43"/>
+    </row>
+    <row r="4" spans="1:4" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="44"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="45"/>
+    </row>
+    <row r="5" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="44"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="45"/>
+    </row>
+    <row r="6" spans="1:4" ht="92.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="44"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="45"/>
+    </row>
+    <row r="7" spans="1:4" ht="339" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="46"/>
+      <c r="B7" s="47"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+    </row>
+    <row r="8" spans="1:4" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="44"/>
-      <c r="C8" s="44"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1410,7 +1418,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97138BF6-410A-40B8-A1ED-211E8B7E2469}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/cronograma_estudo.xlsx
+++ b/cronograma_estudo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Daniel\Desktop\study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31A5A56-0A6A-4FB4-99BD-CA1BD3751B15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A5B6E78-7D9A-46FD-BB77-BDF0F0DD62C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
